--- a/data_folder/tractionmotor/input_data/case.xlsx
+++ b/data_folder/tractionmotor/input_data/case.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,18 @@
       </c>
       <c r="B12" t="n">
         <v>2060</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>scenario_alias</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>*=mix</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data_folder/tractionmotor/input_data/case.xlsx
+++ b/data_folder/tractionmotor/input_data/case.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,10 +553,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>improvement_after_end</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>scenario_alias</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>*=mix</t>
         </is>
